--- a/ky/downloads/data-excel/8.5.2.xlsx
+++ b/ky/downloads/data-excel/8.5.2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15255" windowHeight="11130"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="61">
   <si>
     <t>15-19</t>
   </si>
@@ -391,7 +391,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -451,6 +451,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -757,14 +761,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T43"/>
+  <dimension ref="A1:U45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="35.42578125" customWidth="1"/>
     <col min="3" max="3" width="32.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
@@ -789,7 +793,7 @@
       <c r="P1" s="10"/>
       <c r="Q1" s="10"/>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>17</v>
       </c>
@@ -814,7 +818,7 @@
       <c r="P2" s="10"/>
       <c r="Q2" s="10"/>
     </row>
-    <row r="3" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="5"/>
       <c r="C3" s="6"/>
@@ -832,8 +836,9 @@
       <c r="O3" s="10"/>
       <c r="P3" s="10"/>
       <c r="Q3" s="10"/>
-    </row>
-    <row r="4" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U3" s="10"/>
+    </row>
+    <row r="4" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>12</v>
       </c>
@@ -894,8 +899,11 @@
       <c r="T4" s="9">
         <v>2023</v>
       </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U4" s="9">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>22</v>
       </c>
@@ -956,8 +964,11 @@
       <c r="T5" s="11">
         <v>4.0999999999999996</v>
       </c>
-    </row>
-    <row r="6" spans="1:20" s="26" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U5" s="12">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" s="26" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>14</v>
       </c>
@@ -1018,8 +1029,11 @@
       <c r="T6" s="16">
         <v>5.2</v>
       </c>
-    </row>
-    <row r="7" spans="1:20" s="26" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U6" s="25">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" s="26" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>13</v>
       </c>
@@ -1080,8 +1094,11 @@
       <c r="T7" s="16">
         <v>3.3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U7" s="25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="20" t="s">
         <v>29</v>
       </c>
@@ -1108,8 +1125,9 @@
       <c r="R8" s="20"/>
       <c r="S8" s="18"/>
       <c r="T8" s="18"/>
-    </row>
-    <row r="9" spans="1:20" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U8" s="27"/>
+    </row>
+    <row r="9" spans="1:21" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>32</v>
       </c>
@@ -1170,8 +1188,11 @@
       <c r="T9" s="11">
         <v>5.9</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U9" s="12">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>14</v>
       </c>
@@ -1232,8 +1253,11 @@
       <c r="T10" s="10">
         <v>8.6</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U10" s="13">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>13</v>
       </c>
@@ -1294,8 +1318,11 @@
       <c r="T11" s="10">
         <v>4.7</v>
       </c>
-    </row>
-    <row r="12" spans="1:20" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U11" s="13">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>35</v>
       </c>
@@ -1356,8 +1383,11 @@
       <c r="T12" s="11">
         <v>8.1999999999999993</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U12" s="12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
         <v>14</v>
       </c>
@@ -1418,8 +1448,11 @@
       <c r="T13" s="10">
         <v>14.2</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U13" s="13">
+        <v>10.199999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
         <v>13</v>
       </c>
@@ -1480,8 +1513,11 @@
       <c r="T14" s="10">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U14" s="13">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>38</v>
       </c>
@@ -1542,8 +1578,11 @@
       <c r="T15" s="11">
         <v>5.0999999999999996</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U15" s="12">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
         <v>14</v>
       </c>
@@ -1604,8 +1643,11 @@
       <c r="T16" s="10">
         <v>3.4</v>
       </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U16" s="13">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>13</v>
       </c>
@@ -1666,8 +1708,11 @@
       <c r="T17" s="10">
         <v>6.1</v>
       </c>
-    </row>
-    <row r="18" spans="1:20" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U17" s="13">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
         <v>41</v>
       </c>
@@ -1728,8 +1773,11 @@
       <c r="T18" s="11">
         <v>5.0999999999999996</v>
       </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U18" s="12">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>14</v>
       </c>
@@ -1790,8 +1838,11 @@
       <c r="T19" s="10">
         <v>10.8</v>
       </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U19" s="13">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
         <v>13</v>
       </c>
@@ -1852,8 +1903,11 @@
       <c r="T20" s="10">
         <v>2.2999999999999998</v>
       </c>
-    </row>
-    <row r="21" spans="1:20" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U20" s="13">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>44</v>
       </c>
@@ -1914,8 +1968,11 @@
       <c r="T21" s="11">
         <v>1.4</v>
       </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U21" s="12">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
         <v>14</v>
       </c>
@@ -1976,8 +2033,11 @@
       <c r="T22" s="10">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U22" s="13">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>13</v>
       </c>
@@ -2038,8 +2098,11 @@
       <c r="T23" s="10">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:20" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U23" s="13">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="19" t="s">
         <v>47</v>
       </c>
@@ -2100,8 +2163,11 @@
       <c r="T24" s="11">
         <v>2</v>
       </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U24" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>14</v>
       </c>
@@ -2162,8 +2228,11 @@
       <c r="T25" s="10">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U25" s="13">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
         <v>13</v>
       </c>
@@ -2224,8 +2293,11 @@
       <c r="T26" s="10">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="27" spans="1:20" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U26" s="13">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="19" t="s">
         <v>50</v>
       </c>
@@ -2286,8 +2358,11 @@
       <c r="T27" s="11">
         <v>4.0999999999999996</v>
       </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U27" s="12">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
         <v>14</v>
       </c>
@@ -2348,8 +2423,11 @@
       <c r="T28" s="10">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U28" s="13">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>13</v>
       </c>
@@ -2410,8 +2488,11 @@
       <c r="T29" s="10">
         <v>3.9</v>
       </c>
-    </row>
-    <row r="30" spans="1:20" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U29" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
         <v>53</v>
       </c>
@@ -2472,8 +2553,11 @@
       <c r="T30" s="11">
         <v>3.5</v>
       </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U30" s="12">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>14</v>
       </c>
@@ -2534,8 +2618,11 @@
       <c r="T31" s="10">
         <v>2.6</v>
       </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U31" s="13">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
         <v>13</v>
       </c>
@@ -2596,8 +2683,11 @@
       <c r="T32" s="10">
         <v>4.4000000000000004</v>
       </c>
-    </row>
-    <row r="33" spans="1:20" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U32" s="13">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
         <v>56</v>
       </c>
@@ -2658,8 +2748,11 @@
       <c r="T33" s="11">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U33" s="12">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
         <v>14</v>
       </c>
@@ -2720,8 +2813,11 @@
       <c r="T34" s="10">
         <v>2.7</v>
       </c>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U34" s="13">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>13</v>
       </c>
@@ -2782,8 +2878,11 @@
       <c r="T35" s="10">
         <v>1.8</v>
       </c>
-    </row>
-    <row r="36" spans="1:20" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U35" s="13">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="20" t="s">
         <v>15</v>
       </c>
@@ -2810,8 +2909,9 @@
       <c r="R36" s="20"/>
       <c r="S36" s="18"/>
       <c r="T36" s="18"/>
-    </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U36" s="27"/>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>0</v>
       </c>
@@ -2872,8 +2972,11 @@
       <c r="T37" s="10">
         <v>6.7</v>
       </c>
-    </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U37" s="13">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
         <v>1</v>
       </c>
@@ -2934,8 +3037,11 @@
       <c r="T38" s="10">
         <v>8.1999999999999993</v>
       </c>
-    </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U38" s="13">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>2</v>
       </c>
@@ -2996,8 +3102,11 @@
       <c r="T39" s="10">
         <v>3.4</v>
       </c>
-    </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U39" s="13">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
         <v>3</v>
       </c>
@@ -3058,8 +3167,11 @@
       <c r="T40" s="10">
         <v>2.7</v>
       </c>
-    </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U40" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
         <v>4</v>
       </c>
@@ -3120,8 +3232,11 @@
       <c r="T41" s="10">
         <v>1.8</v>
       </c>
-    </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U41" s="13">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
         <v>5</v>
       </c>
@@ -3182,8 +3297,11 @@
       <c r="T42" s="10">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U42" s="13">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>11</v>
       </c>
@@ -3243,6 +3361,19 @@
       </c>
       <c r="T43" s="17" t="s">
         <v>7</v>
+      </c>
+      <c r="U43" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="U44" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U45" s="28">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
